--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 16.1%  (9W / 47L of 56 evaluated)</t>
+          <t>Win Rate: 21.4%  (12W / 44L of 56 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2580</v>
+        <v>2550</v>
       </c>
       <c r="D6" t="n">
         <v>2540</v>
@@ -595,10 +595,10 @@
         <v>2620</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.55</v>
+        <v>-0.39</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4760</v>
+        <v>4740</v>
       </c>
       <c r="D7" t="n">
         <v>4620</v>
@@ -637,10 +637,10 @@
         <v>4860</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.94</v>
+        <v>-2.53</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2160</v>
+        <v>2300</v>
       </c>
       <c r="D9" t="n">
         <v>2370</v>
@@ -721,10 +721,10 @@
         <v>2370</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
         <v>332</v>
@@ -763,10 +763,10 @@
         <v>344</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.49</v>
+        <v>-2.35</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>176</v>
@@ -805,10 +805,10 @@
         <v>195</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.72</v>
+        <v>4.28</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.38</v>
+        <v>-5.88</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>150</v>
@@ -847,10 +847,10 @@
         <v>155</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.96</v>
+        <v>-1.32</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2840</v>
+        <v>2820</v>
       </c>
       <c r="D18" t="n">
         <v>2680</v>
@@ -1099,10 +1099,10 @@
         <v>2960</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.23</v>
+        <v>4.96</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.63</v>
+        <v>-4.96</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D22" t="n">
         <v>71</v>
@@ -1267,10 +1267,10 @@
         <v>71</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>725</v>
+        <v>710.47</v>
       </c>
       <c r="D23" t="n">
         <v>715</v>
@@ -1309,14 +1309,14 @@
         <v>730</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.64</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8475</v>
+        <v>7125</v>
       </c>
       <c r="D25" t="n">
         <v>6500</v>
@@ -1393,10 +1393,10 @@
         <v>8475</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>18.95</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-23.3</v>
+        <v>-8.77</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D26" t="n">
         <v>478</v>
@@ -1435,10 +1435,10 @@
         <v>500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.4</v>
+        <v>-4.78</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D27" t="n">
         <v>109</v>
@@ -1477,10 +1477,10 @@
         <v>111</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.73</v>
+        <v>11</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.81</v>
+        <v>9</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" t="n">
         <v>87</v>
@@ -1519,10 +1519,10 @@
         <v>96</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.87</v>
+        <v>9.09</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.25</v>
+        <v>-1.14</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D32" t="n">
         <v>174</v>
@@ -1687,10 +1687,10 @@
         <v>200</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>24.22</v>
+        <v>23.46</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.07</v>
+        <v>7.41</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D34" t="n">
         <v>322</v>
@@ -1771,10 +1771,10 @@
         <v>332</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-3.01</v>
+        <v>-1.23</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="D35" t="n">
         <v>720</v>
@@ -1813,10 +1813,10 @@
         <v>775</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>-3.12</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.1</v>
+        <v>-10</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D37" t="n">
         <v>197</v>
@@ -1897,10 +1897,10 @@
         <v>214</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>-1.83</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-7.94</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D38" t="n">
         <v>178</v>
@@ -1939,10 +1939,10 @@
         <v>193</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-7.77</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3888.02</v>
+        <v>4090</v>
       </c>
       <c r="D41" t="n">
         <v>3850</v>
@@ -2065,10 +2065,10 @@
         <v>3983.09</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2.44</v>
+        <v>-2.61</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.98</v>
+        <v>-5.87</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3210</v>
+        <v>3190</v>
       </c>
       <c r="D42" t="n">
         <v>2760</v>
@@ -2107,10 +2107,10 @@
         <v>3260</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.56</v>
+        <v>2.19</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-14.02</v>
+        <v>-13.48</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D43" t="n">
         <v>416</v>
@@ -2149,14 +2149,14 @@
         <v>424</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.95</v>
+        <v>2.42</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.48</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D46" t="n">
         <v>416</v>
@@ -2275,10 +2275,10 @@
         <v>432</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5.37</v>
+        <v>4.85</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1.46</v>
+        <v>0.97</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
         <v>39</v>
@@ -2317,10 +2317,10 @@
         <v>42</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0</v>
+        <v>-2.33</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-7.14</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D49" t="n">
         <v>90</v>
@@ -2401,10 +2401,10 @@
         <v>118</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>18</v>
+        <v>20.41</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-10</v>
+        <v>-8.16</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D50" t="n">
         <v>360</v>
@@ -2443,10 +2443,10 @@
         <v>408</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4.62</v>
+        <v>7.37</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-7.69</v>
+        <v>-5.26</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D51" t="n">
         <v>272</v>
@@ -2485,10 +2485,10 @@
         <v>284</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-4.23</v>
+        <v>-4.9</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="D55" t="n">
         <v>505</v>
@@ -2653,14 +2653,14 @@
         <v>515</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="D56" t="n">
         <v>338</v>
@@ -2695,10 +2695,10 @@
         <v>338</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0</v>
+        <v>-14.65</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0</v>
+        <v>-14.65</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="D57" t="n">
         <v>910</v>
@@ -2737,10 +2737,10 @@
         <v>1005</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="D58" t="n">
         <v>380</v>
@@ -2779,10 +2779,10 @@
         <v>505</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>16.9</v>
+        <v>20.81</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-12.04</v>
+        <v>-9.09</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D59" t="n">
         <v>159</v>
@@ -2821,10 +2821,10 @@
         <v>173</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.37</v>
+        <v>2.98</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-5.92</v>
+        <v>-5.36</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D60" t="n">
         <v>565</v>
@@ -2863,10 +2863,10 @@
         <v>625</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-8.869999999999999</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-05-20</t>
+          <t>Swing — Review sesi market 2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 21.4%  (12W / 44L of 56 evaluated)</t>
+          <t>Win Rate: 34.8%  (24W / 45L of 69 evaluated)</t>
         </is>
       </c>
     </row>
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D5" t="n">
         <v>1390</v>
       </c>
-      <c r="D5" t="n">
-        <v>1340</v>
-      </c>
       <c r="E5" t="n">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-3.6</v>
+        <v>-0.71</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AUTO.JK</t>
+          <t>ALDO.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2550</v>
+        <v>695</v>
       </c>
       <c r="D6" t="n">
-        <v>2540</v>
+        <v>700</v>
       </c>
       <c r="E6" t="n">
-        <v>2620</v>
+        <v>700</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.75</v>
+        <v>0.72</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.72</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BDMN.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,28 +628,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4740</v>
+        <v>5950</v>
       </c>
       <c r="D7" t="n">
-        <v>4620</v>
+        <v>5975</v>
       </c>
       <c r="E7" t="n">
-        <v>4860</v>
+        <v>6100</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.42</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -661,37 +661,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRAM.JK</t>
+          <t>AUTO.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>PRE_MARKUP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4740</v>
+        <v>2580</v>
       </c>
       <c r="D8" t="n">
-        <v>4770</v>
+        <v>2550</v>
       </c>
       <c r="E8" t="n">
-        <v>4790</v>
+        <v>2630</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.16</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTPN.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,19 +712,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2300</v>
+        <v>4410</v>
       </c>
       <c r="D9" t="n">
-        <v>2370</v>
+        <v>4740</v>
       </c>
       <c r="E9" t="n">
-        <v>2370</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.04</v>
+        <v>13.38</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.04</v>
+        <v>7.48</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CFIN.JK</t>
+          <t>BIPI.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>340</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>332</v>
+        <v>202</v>
       </c>
       <c r="E10" t="n">
-        <v>344</v>
+        <v>212</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.18</v>
+        <v>3.92</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.35</v>
+        <v>-0.98</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CINT.JK</t>
+          <t>BJBR.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>765</v>
       </c>
       <c r="D11" t="n">
-        <v>176</v>
+        <v>760</v>
       </c>
       <c r="E11" t="n">
-        <v>195</v>
+        <v>775</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.28</v>
+        <v>1.31</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-5.88</v>
+        <v>-0.65</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DMAS.JK</t>
+          <t>BNGA.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>1655</v>
       </c>
       <c r="D12" t="n">
-        <v>150</v>
+        <v>1645</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>1670</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.97</v>
+        <v>0.91</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.32</v>
+        <v>-0.6</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DYAN.JK</t>
+          <t>BTPN.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>2240</v>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>2300</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>2330</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.41</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.68</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EPMT.JK</t>
+          <t>CFIN.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2230</v>
+        <v>338</v>
       </c>
       <c r="D14" t="n">
-        <v>2260</v>
+        <v>340</v>
       </c>
       <c r="E14" t="n">
-        <v>2260</v>
+        <v>344</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.35</v>
+        <v>0.59</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GGRM.JK</t>
+          <t>DGIK.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16350</v>
+        <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v>16200</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>16650</v>
+        <v>137</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.83</v>
+        <v>3.01</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GSMF.JK</t>
+          <t>DMAS.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1006,28 +1006,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-14.16</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.66</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ISAT.JK</t>
+          <t>EPMT.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1048,19 +1048,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2150</v>
+        <v>2380</v>
       </c>
       <c r="D17" t="n">
-        <v>2080</v>
+        <v>2230</v>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>2410</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.26</v>
+        <v>-6.3</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KONI.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2820</v>
+        <v>1240</v>
       </c>
       <c r="D18" t="n">
-        <v>2680</v>
+        <v>1225</v>
       </c>
       <c r="E18" t="n">
-        <v>2960</v>
+        <v>1310</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.96</v>
+        <v>5.65</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.96</v>
+        <v>-1.21</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>GGRM.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1132,28 +1132,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1480</v>
+        <v>16800</v>
       </c>
       <c r="D19" t="n">
-        <v>1485</v>
+        <v>16350</v>
       </c>
       <c r="E19" t="n">
-        <v>1495</v>
+        <v>17975</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.01</v>
+        <v>6.99</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.68</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PGLI.JK</t>
+          <t>GSMF.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="D20" t="n">
-        <v>208</v>
+        <v>113</v>
       </c>
       <c r="E20" t="n">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.619999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>-14.39</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RELI.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>510</v>
+        <v>125</v>
       </c>
       <c r="D21" t="n">
-        <v>486</v>
+        <v>114</v>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>126</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.71</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JGLE.JK</t>
+          <t>ISAT.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>2220</v>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>2150</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>2250</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.970000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-8.970000000000001</v>
+        <v>-3.15</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>POWR.JK</t>
+          <t>KAEF.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1300,28 +1300,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>710.47</v>
+        <v>550</v>
       </c>
       <c r="D23" t="n">
-        <v>715</v>
+        <v>505</v>
       </c>
       <c r="E23" t="n">
-        <v>730</v>
+        <v>550</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-8.18</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2630</v>
+        <v>1480</v>
       </c>
       <c r="D24" t="n">
-        <v>2550</v>
+        <v>1480</v>
       </c>
       <c r="E24" t="n">
-        <v>2640</v>
+        <v>1485</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,28 +1384,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7125</v>
+        <v>995</v>
       </c>
       <c r="D25" t="n">
-        <v>6500</v>
+        <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>8475</v>
+        <v>1005</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>18.95</v>
+        <v>1.01</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.77</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PBID.JK</t>
+          <t>PNLF.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1426,19 +1426,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>502</v>
+        <v>254</v>
       </c>
       <c r="D26" t="n">
-        <v>478</v>
+        <v>250</v>
       </c>
       <c r="E26" t="n">
-        <v>500</v>
+        <v>256</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4</v>
+        <v>0.79</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.78</v>
+        <v>-1.57</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DFAM.JK</t>
+          <t>SMSM.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1468,28 +1468,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100</v>
+        <v>1785</v>
       </c>
       <c r="D27" t="n">
-        <v>109</v>
+        <v>1735</v>
       </c>
       <c r="E27" t="n">
-        <v>111</v>
+        <v>1785</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.8</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PRIM.JK</t>
+          <t>SRSN.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D28" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.09</v>
+        <v>1.45</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.14</v>
+        <v>-1.45</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BPTR.JK</t>
+          <t>DPUM.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1552,28 +1552,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.13</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LUCK.JK</t>
+          <t>JGLE.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1594,19 +1594,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFAN.JK</t>
+          <t>OASA.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,28 +1636,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1955</v>
+        <v>394</v>
       </c>
       <c r="D31" t="n">
-        <v>1955</v>
+        <v>426</v>
       </c>
       <c r="E31" t="n">
-        <v>1955</v>
+        <v>430</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>POWR.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>162</v>
+        <v>760</v>
       </c>
       <c r="D32" t="n">
-        <v>174</v>
+        <v>710.47</v>
       </c>
       <c r="E32" t="n">
-        <v>200</v>
+        <v>724.5</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>23.46</v>
+        <v>-4.67</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-6.52</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMKL.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1720,28 +1720,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>161</v>
+        <v>2600</v>
       </c>
       <c r="D33" t="n">
-        <v>155</v>
+        <v>2630</v>
       </c>
       <c r="E33" t="n">
-        <v>164</v>
+        <v>2640</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.15</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1753,7 +1753,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GGRP.JK</t>
+          <t>MPOW.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>326</v>
+        <v>120</v>
       </c>
       <c r="D34" t="n">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E34" t="n">
-        <v>332</v>
+        <v>148</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.84</v>
+        <v>23.33</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.67</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PGJO.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1804,28 +1804,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>800</v>
+        <v>735</v>
       </c>
       <c r="D35" t="n">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="E35" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.12</v>
+        <v>10.88</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>10.2</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PURA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1846,28 +1846,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>44</v>
+        <v>5950</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>7125</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>7125</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-9.09</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>19.75</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1879,28 +1879,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TAMA.JK</t>
+          <t>PBID.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>218</v>
+        <v>555</v>
       </c>
       <c r="D37" t="n">
-        <v>197</v>
+        <v>502</v>
       </c>
       <c r="E37" t="n">
-        <v>214</v>
+        <v>502</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>-1.83</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PPGL.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1930,19 +1930,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="D38" t="n">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="E38" t="n">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-2.03</v>
+        <v>-2.78</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-9.640000000000001</v>
+        <v>-7.41</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PNGO.JK</t>
+          <t>PRIM.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1972,19 +1972,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3390</v>
+        <v>87</v>
       </c>
       <c r="D39" t="n">
-        <v>3400</v>
+        <v>88</v>
       </c>
       <c r="E39" t="n">
-        <v>3490</v>
+        <v>92</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.29</v>
+        <v>1.15</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2005,37 +2005,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>BPTR.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>222</v>
+        <v>83</v>
       </c>
       <c r="D40" t="n">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="E40" t="n">
-        <v>230</v>
+        <v>86</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4.82</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MCOL.JK</t>
+          <t>SFAN.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2056,28 +2056,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4090</v>
+        <v>1945</v>
       </c>
       <c r="D41" t="n">
-        <v>3850</v>
+        <v>1955</v>
       </c>
       <c r="E41" t="n">
-        <v>3983.09</v>
+        <v>1955</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-2.61</v>
+        <v>0.51</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-5.87</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.51</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>KJEN.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2098,19 +2098,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3190</v>
+        <v>167</v>
       </c>
       <c r="D42" t="n">
-        <v>2760</v>
+        <v>162</v>
       </c>
       <c r="E42" t="n">
-        <v>3260</v>
+        <v>168</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2.19</v>
+        <v>0.6</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-13.48</v>
+        <v>-2.99</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>SMKL.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>414</v>
+        <v>168</v>
       </c>
       <c r="D43" t="n">
-        <v>416</v>
+        <v>161</v>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2.42</v>
+        <v>7.14</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4.17</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DRMA.JK</t>
+          <t>GGRP.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2182,19 +2182,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>990</v>
+        <v>326</v>
       </c>
       <c r="D44" t="n">
-        <v>980</v>
+        <v>326</v>
       </c>
       <c r="E44" t="n">
-        <v>1000</v>
+        <v>338</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.01</v>
+        <v>3.68</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NTBK.JK</t>
+          <t>PGJO.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>97</v>
+        <v>855</v>
       </c>
       <c r="D45" t="n">
-        <v>83</v>
+        <v>800</v>
       </c>
       <c r="E45" t="n">
-        <v>99</v>
+        <v>825</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.06</v>
+        <v>-3.51</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-14.43</v>
+        <v>-6.43</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>PURA.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>412</v>
+        <v>40</v>
       </c>
       <c r="D46" t="n">
-        <v>416</v>
+        <v>44</v>
       </c>
       <c r="E46" t="n">
-        <v>432</v>
+        <v>44</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4.85</v>
+        <v>10</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.97</v>
+        <v>10</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KKES.JK</t>
+          <t>TAMA.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2308,19 +2308,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-2.33</v>
+        <v>-0.85</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.84</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ELPI.JK</t>
+          <t>PNGO.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2350,28 +2350,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1425</v>
+        <v>3380</v>
       </c>
       <c r="D48" t="n">
-        <v>1380</v>
+        <v>3390</v>
       </c>
       <c r="E48" t="n">
-        <v>1445</v>
+        <v>3570</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1.4</v>
+        <v>5.62</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.3</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ENZO.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D49" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E49" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>20.41</v>
+        <v>4.55</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-8.16</v>
+        <v>0</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2434,19 +2434,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="D50" t="n">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="E50" t="n">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>7.37</v>
+        <v>0.47</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-5.26</v>
+        <v>-2.82</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2467,7 +2467,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>DRMA.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2476,19 +2476,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>286</v>
+        <v>1000</v>
       </c>
       <c r="D51" t="n">
-        <v>272</v>
+        <v>990</v>
       </c>
       <c r="E51" t="n">
-        <v>284</v>
+        <v>1005</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-4.9</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>NTBK.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2518,19 +2518,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D52" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
         <v>104</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-5</v>
+        <v>-6.73</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HYGN.JK</t>
+          <t>SWID.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2560,28 +2560,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="D53" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E53" t="n">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1.96</v>
+        <v>6.06</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.02</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LABS.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D54" t="n">
-        <v>153</v>
+        <v>412</v>
       </c>
       <c r="E54" t="n">
-        <v>184</v>
+        <v>416</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>13.58</v>
+        <v>0.97</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-5.56</v>
+        <v>0</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2635,37 +2635,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>KKES.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>500</v>
+        <v>47</v>
       </c>
       <c r="D55" t="n">
-        <v>505</v>
+        <v>43</v>
       </c>
       <c r="E55" t="n">
-        <v>515</v>
+        <v>45</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3</v>
+        <v>-4.26</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-8.51</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2677,7 +2677,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>ELPI.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2686,19 +2686,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>396</v>
+        <v>1530</v>
       </c>
       <c r="D56" t="n">
-        <v>338</v>
+        <v>1425</v>
       </c>
       <c r="E56" t="n">
-        <v>338</v>
+        <v>1510</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-14.65</v>
+        <v>-1.31</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-14.65</v>
+        <v>-6.86</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FORE.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D57" t="n">
-        <v>910</v>
+        <v>98</v>
       </c>
       <c r="E57" t="n">
-        <v>1005</v>
+        <v>105</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASPI.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2770,28 +2770,28 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>418</v>
+        <v>370</v>
       </c>
       <c r="D58" t="n">
         <v>380</v>
       </c>
       <c r="E58" t="n">
-        <v>505</v>
+        <v>380</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>20.81</v>
+        <v>2.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-9.09</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.7</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2803,7 +2803,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CGAS.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>168</v>
+        <v>845</v>
       </c>
       <c r="D59" t="n">
-        <v>159</v>
+        <v>815</v>
       </c>
       <c r="E59" t="n">
-        <v>173</v>
+        <v>850</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.98</v>
+        <v>0.59</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-5.36</v>
+        <v>-3.55</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -2845,40 +2845,586 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>MPXL.JK</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>158</v>
+      </c>
+      <c r="D60" t="n">
+        <v>150</v>
+      </c>
+      <c r="E60" t="n">
+        <v>158</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RGAS.JK</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>99</v>
+      </c>
+      <c r="D61" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" t="n">
+        <v>102</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SURI.JK</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>73</v>
+      </c>
+      <c r="D62" t="n">
+        <v>72</v>
+      </c>
+      <c r="E62" t="n">
+        <v>75</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HYGN.JK</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>156</v>
+      </c>
+      <c r="D63" t="n">
+        <v>153</v>
+      </c>
+      <c r="E63" t="n">
+        <v>156</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BAIK.JK</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>545</v>
+      </c>
+      <c r="D64" t="n">
+        <v>600</v>
+      </c>
+      <c r="E64" t="n">
+        <v>625</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>171</v>
+      </c>
+      <c r="D65" t="n">
+        <v>162</v>
+      </c>
+      <c r="E65" t="n">
+        <v>174</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NEST.JK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>515</v>
+      </c>
+      <c r="D66" t="n">
+        <v>500</v>
+      </c>
+      <c r="E66" t="n">
+        <v>525</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>KSIX.JK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>330</v>
+      </c>
+      <c r="D67" t="n">
+        <v>344</v>
+      </c>
+      <c r="E67" t="n">
+        <v>350</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ASPR.JK</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>464</v>
+      </c>
+      <c r="D68" t="n">
+        <v>396</v>
+      </c>
+      <c r="E68" t="n">
+        <v>540</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-14.66</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DKHH.JK</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>73</v>
+      </c>
+      <c r="D69" t="n">
+        <v>70</v>
+      </c>
+      <c r="E69" t="n">
+        <v>74</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ASPI.JK</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>432</v>
+      </c>
+      <c r="D70" t="n">
+        <v>418</v>
+      </c>
+      <c r="E70" t="n">
+        <v>478</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CGAS.JK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>174</v>
+      </c>
+      <c r="D71" t="n">
+        <v>168</v>
+      </c>
+      <c r="E71" t="n">
+        <v>176</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FAPA.JK</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>7175</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E72" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>KETR.JK</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>PRE_MARKUP</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>585</v>
+      </c>
+      <c r="D73" t="n">
         <v>615</v>
       </c>
-      <c r="D60" t="n">
-        <v>565</v>
-      </c>
-      <c r="E60" t="n">
-        <v>625</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="E73" t="n">
+        <v>620</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2913,7 +3459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-05-20</t>
+          <t>Scalping — Review sesi market 2026-05-20</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -731,12 +757,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -941,12 +992,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1025,12 +1086,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1062,17 +1128,22 @@
       <c r="G17" s="4" t="n">
         <v>-6.3</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1104,17 +1175,22 @@
       <c r="G18" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>-2.68</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1193,12 +1274,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1272,17 +1363,22 @@
       <c r="G22" s="4" t="n">
         <v>-3.15</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1319,12 +1415,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,12 +1509,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>-1.57</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1487,12 +1603,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>-1.45</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1571,12 +1697,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1613,12 +1744,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1655,12 +1791,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1697,12 +1838,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1739,12 +1885,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1781,12 +1932,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1823,12 +1979,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1865,12 +2026,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1907,12 +2073,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1949,12 +2120,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1991,12 +2167,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2028,17 +2209,22 @@
       <c r="G40" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2075,12 +2261,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2112,17 +2303,22 @@
       <c r="G42" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2154,17 +2350,22 @@
       <c r="G43" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2196,17 +2397,22 @@
       <c r="G44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2243,12 +2449,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2285,12 +2496,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2327,12 +2543,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2369,12 +2590,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2406,17 +2632,22 @@
       <c r="G49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2448,17 +2679,22 @@
       <c r="G50" s="4" t="n">
         <v>-2.82</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2490,17 +2726,22 @@
       <c r="G51" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2537,12 +2778,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2579,12 +2825,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2616,17 +2867,22 @@
       <c r="G54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2663,12 +2919,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2705,12 +2966,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2742,17 +3008,22 @@
       <c r="G57" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2789,12 +3060,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2826,17 +3102,22 @@
       <c r="G59" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2873,12 +3154,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2915,12 +3201,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2952,17 +3243,22 @@
       <c r="G62" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2999,12 +3295,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3041,12 +3342,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3078,17 +3384,22 @@
       <c r="G65" s="4" t="n">
         <v>-5.26</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3120,17 +3431,22 @@
       <c r="G66" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3167,12 +3483,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3204,17 +3525,22 @@
       <c r="G68" s="4" t="n">
         <v>-14.66</v>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3246,17 +3572,22 @@
       <c r="G69" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3288,17 +3619,22 @@
       <c r="G70" s="4" t="n">
         <v>-3.24</v>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,17 +3666,22 @@
       <c r="G71" s="4" t="n">
         <v>-3.45</v>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,12 +3718,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3419,12 +3765,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3441,7 +3792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3451,9 +3802,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3483,7 +3835,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3508,15 +3860,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-20.xlsx
+++ b/data/performance/daily/signal_list_2026-05-20.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1400</v>
       </c>
       <c r="D5" t="n">
+        <v>1360</v>
+      </c>
+      <c r="E5" t="n">
         <v>1390</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1400</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>695</v>
       </c>
       <c r="D6" t="n">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="E6" t="n">
         <v>700</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.72</v>
+      <c r="F6" t="n">
+        <v>700</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>0.72</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>5950</v>
       </c>
       <c r="D7" t="n">
+        <v>5950</v>
+      </c>
+      <c r="E7" t="n">
         <v>5975</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>6100</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.52</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>2580</v>
       </c>
       <c r="D8" t="n">
+        <v>2580</v>
+      </c>
+      <c r="E8" t="n">
         <v>2550</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2630</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.94</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>4410</v>
       </c>
       <c r="D9" t="n">
+        <v>4410</v>
+      </c>
+      <c r="E9" t="n">
         <v>4740</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>5000</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>13.38</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>7.48</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>204</v>
       </c>
       <c r="D10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" t="n">
         <v>202</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>212</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>3.92</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>765</v>
       </c>
       <c r="D11" t="n">
+        <v>765</v>
+      </c>
+      <c r="E11" t="n">
         <v>760</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>775</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1655</v>
       </c>
       <c r="D12" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E12" t="n">
         <v>1645</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1670</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>2240</v>
       </c>
       <c r="D13" t="n">
+        <v>2190</v>
+      </c>
+      <c r="E13" t="n">
         <v>2300</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2330</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>4.02</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>2.68</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>338</v>
       </c>
       <c r="D14" t="n">
+        <v>338</v>
+      </c>
+      <c r="E14" t="n">
         <v>340</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>344</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1026,30 +1062,33 @@
         <v>133</v>
       </c>
       <c r="E15" t="n">
+        <v>133</v>
+      </c>
+      <c r="F15" t="n">
         <v>137</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3.01</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>151</v>
       </c>
       <c r="D16" t="n">
+        <v>151</v>
+      </c>
+      <c r="E16" t="n">
         <v>152</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>153</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>2380</v>
       </c>
       <c r="D17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E17" t="n">
         <v>2230</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2410</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-6.3</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>1240</v>
       </c>
       <c r="D18" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E18" t="n">
         <v>1225</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1310</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>5.65</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>16800</v>
       </c>
       <c r="D19" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E19" t="n">
         <v>16350</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>17975</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>6.99</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-2.68</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>132</v>
       </c>
       <c r="D20" t="n">
+        <v>115</v>
+      </c>
+      <c r="E20" t="n">
         <v>113</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>120</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-14.39</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>125</v>
       </c>
       <c r="D21" t="n">
+        <v>125</v>
+      </c>
+      <c r="E21" t="n">
         <v>114</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>126</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>2220</v>
       </c>
       <c r="D22" t="n">
+        <v>2180</v>
+      </c>
+      <c r="E22" t="n">
         <v>2150</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2250</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-3.15</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>550</v>
       </c>
       <c r="D23" t="n">
+        <v>545</v>
+      </c>
+      <c r="E23" t="n">
         <v>505</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>550</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-8.18</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1449,30 +1512,33 @@
         <v>1480</v>
       </c>
       <c r="E24" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F24" t="n">
         <v>1485</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1496,30 +1562,33 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F25" t="n">
         <v>1005</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1543,30 +1612,33 @@
         <v>250</v>
       </c>
       <c r="E26" t="n">
+        <v>250</v>
+      </c>
+      <c r="F26" t="n">
         <v>256</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-1.57</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>1785</v>
       </c>
       <c r="D27" t="n">
+        <v>1785</v>
+      </c>
+      <c r="E27" t="n">
         <v>1735</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>1785</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1637,30 +1712,33 @@
         <v>68</v>
       </c>
       <c r="E28" t="n">
+        <v>68</v>
+      </c>
+      <c r="F28" t="n">
         <v>70</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-1.45</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1684,30 +1762,33 @@
         <v>204</v>
       </c>
       <c r="E29" t="n">
+        <v>204</v>
+      </c>
+      <c r="F29" t="n">
         <v>216</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1733,28 +1814,31 @@
       <c r="E30" t="n">
         <v>78</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>-9.300000000000001</v>
+      <c r="F30" t="n">
+        <v>78</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H30" s="4" t="n">
+        <v>-9.300000000000001</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>394</v>
       </c>
       <c r="D31" t="n">
+        <v>390</v>
+      </c>
+      <c r="E31" t="n">
         <v>426</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>430</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>760</v>
       </c>
       <c r="D32" t="n">
+        <v>705.8</v>
+      </c>
+      <c r="E32" t="n">
         <v>710.47</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>724.5</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>-4.67</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-6.52</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>2600</v>
       </c>
       <c r="D33" t="n">
+        <v>2640</v>
+      </c>
+      <c r="E33" t="n">
         <v>2630</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>2640</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>120</v>
       </c>
       <c r="D34" t="n">
+        <v>119</v>
+      </c>
+      <c r="E34" t="n">
         <v>128</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>148</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>23.33</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>735</v>
       </c>
       <c r="D35" t="n">
+        <v>770</v>
+      </c>
+      <c r="E35" t="n">
         <v>810</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>815</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>10.88</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>10.2</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>5950</v>
       </c>
       <c r="D36" t="n">
-        <v>7125</v>
+        <v>5950</v>
       </c>
       <c r="E36" t="n">
         <v>7125</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>19.75</v>
+      <c r="F36" t="n">
+        <v>7125</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>19.75</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H36" s="4" t="n">
+        <v>19.75</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2062,28 +2164,31 @@
       <c r="E37" t="n">
         <v>502</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>-9.550000000000001</v>
+      <c r="F37" t="n">
+        <v>502</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>-9.550000000000001</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H37" s="4" t="n">
+        <v>-9.550000000000001</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>108</v>
       </c>
       <c r="D38" t="n">
+        <v>101</v>
+      </c>
+      <c r="E38" t="n">
         <v>100</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>105</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-7.41</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2151,33 +2259,36 @@
         <v>87</v>
       </c>
       <c r="D39" t="n">
+        <v>87</v>
+      </c>
+      <c r="E39" t="n">
         <v>88</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>92</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>5.75</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>83</v>
       </c>
       <c r="D40" t="n">
+        <v>84</v>
+      </c>
+      <c r="E40" t="n">
         <v>79</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>86</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>3.61</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>1945</v>
       </c>
       <c r="D41" t="n">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="E41" t="n">
         <v>1955</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>0.51</v>
+      <c r="F41" t="n">
+        <v>1955</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H41" s="4" t="n">
+        <v>0.51</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>167</v>
       </c>
       <c r="D42" t="n">
+        <v>167</v>
+      </c>
+      <c r="E42" t="n">
         <v>162</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>168</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>168</v>
       </c>
       <c r="D43" t="n">
+        <v>170</v>
+      </c>
+      <c r="E43" t="n">
         <v>161</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>180</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>326</v>
       </c>
       <c r="D44" t="n">
+        <v>332</v>
+      </c>
+      <c r="E44" t="n">
         <v>326</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>338</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>3.68</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2433,33 +2559,36 @@
         <v>855</v>
       </c>
       <c r="D45" t="n">
+        <v>820</v>
+      </c>
+      <c r="E45" t="n">
         <v>800</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>825</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>-3.51</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-6.43</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2485,28 +2614,31 @@
       <c r="E46" t="n">
         <v>44</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>10</v>
+      <c r="F46" t="n">
+        <v>44</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H46" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2527,33 +2659,36 @@
         <v>234</v>
       </c>
       <c r="D47" t="n">
+        <v>232</v>
+      </c>
+      <c r="E47" t="n">
         <v>218</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>232</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>-6.84</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,33 +2709,36 @@
         <v>3380</v>
       </c>
       <c r="D48" t="n">
+        <v>3420</v>
+      </c>
+      <c r="E48" t="n">
         <v>3390</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>3570</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>5.62</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,33 +2759,36 @@
         <v>88</v>
       </c>
       <c r="D49" t="n">
+        <v>89</v>
+      </c>
+      <c r="E49" t="n">
         <v>88</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>92</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>4.55</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,33 +2809,36 @@
         <v>426</v>
       </c>
       <c r="D50" t="n">
+        <v>426</v>
+      </c>
+      <c r="E50" t="n">
         <v>414</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>428</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-2.82</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2715,33 +2859,36 @@
         <v>1000</v>
       </c>
       <c r="D51" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E51" t="n">
         <v>990</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>1005</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2762,33 +2909,36 @@
         <v>104</v>
       </c>
       <c r="D52" t="n">
+        <v>104</v>
+      </c>
+      <c r="E52" t="n">
         <v>97</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>104</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-6.73</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2809,33 +2959,36 @@
         <v>99</v>
       </c>
       <c r="D53" t="n">
+        <v>102</v>
+      </c>
+      <c r="E53" t="n">
         <v>101</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>105</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2856,33 +3009,36 @@
         <v>412</v>
       </c>
       <c r="D54" t="n">
+        <v>414</v>
+      </c>
+      <c r="E54" t="n">
         <v>412</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>416</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2903,33 +3059,36 @@
         <v>47</v>
       </c>
       <c r="D55" t="n">
+        <v>45</v>
+      </c>
+      <c r="E55" t="n">
         <v>43</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>45</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>-4.26</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>-8.51</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2950,33 +3109,36 @@
         <v>1530</v>
       </c>
       <c r="D56" t="n">
+        <v>1470</v>
+      </c>
+      <c r="E56" t="n">
         <v>1425</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>1510</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>-1.31</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>-6.86</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2997,33 +3159,36 @@
         <v>100</v>
       </c>
       <c r="D57" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" t="n">
         <v>98</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>105</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,33 +3209,36 @@
         <v>370</v>
       </c>
       <c r="D58" t="n">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="E58" t="n">
         <v>380</v>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>2.7</v>
+      <c r="F58" t="n">
+        <v>380</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H58" s="4" t="n">
+        <v>2.7</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,33 +3259,36 @@
         <v>845</v>
       </c>
       <c r="D59" t="n">
+        <v>845</v>
+      </c>
+      <c r="E59" t="n">
         <v>815</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>850</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3138,33 +3309,36 @@
         <v>158</v>
       </c>
       <c r="D60" t="n">
+        <v>155</v>
+      </c>
+      <c r="E60" t="n">
         <v>150</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>158</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>-5.06</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3185,33 +3359,36 @@
         <v>99</v>
       </c>
       <c r="D61" t="n">
+        <v>99</v>
+      </c>
+      <c r="E61" t="n">
         <v>100</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>102</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>3.03</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3232,33 +3409,36 @@
         <v>73</v>
       </c>
       <c r="D62" t="n">
+        <v>74</v>
+      </c>
+      <c r="E62" t="n">
         <v>72</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>75</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>2.74</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3279,33 +3459,36 @@
         <v>156</v>
       </c>
       <c r="D63" t="n">
+        <v>155</v>
+      </c>
+      <c r="E63" t="n">
         <v>153</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>156</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3326,33 +3509,36 @@
         <v>545</v>
       </c>
       <c r="D64" t="n">
+        <v>545</v>
+      </c>
+      <c r="E64" t="n">
         <v>600</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>625</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>14.68</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>10.09</v>
       </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3373,33 +3559,36 @@
         <v>171</v>
       </c>
       <c r="D65" t="n">
+        <v>172</v>
+      </c>
+      <c r="E65" t="n">
         <v>162</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>174</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>-5.26</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3420,33 +3609,36 @@
         <v>515</v>
       </c>
       <c r="D66" t="n">
+        <v>520</v>
+      </c>
+      <c r="E66" t="n">
         <v>500</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>525</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="G66" s="4" t="n">
         <v>1.94</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3467,33 +3659,36 @@
         <v>330</v>
       </c>
       <c r="D67" t="n">
+        <v>324</v>
+      </c>
+      <c r="E67" t="n">
         <v>344</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>350</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3514,33 +3709,36 @@
         <v>464</v>
       </c>
       <c r="D68" t="n">
+        <v>470</v>
+      </c>
+      <c r="E68" t="n">
         <v>396</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>540</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="G68" s="4" t="n">
         <v>16.38</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="H68" s="4" t="n">
         <v>-14.66</v>
       </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3561,33 +3759,36 @@
         <v>73</v>
       </c>
       <c r="D69" t="n">
+        <v>71</v>
+      </c>
+      <c r="E69" t="n">
         <v>70</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>74</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3608,33 +3809,36 @@
         <v>432</v>
       </c>
       <c r="D70" t="n">
+        <v>458</v>
+      </c>
+      <c r="E70" t="n">
         <v>418</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>478</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="G70" s="4" t="n">
         <v>10.65</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>-3.24</v>
       </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3655,33 +3859,36 @@
         <v>174</v>
       </c>
       <c r="D71" t="n">
+        <v>176</v>
+      </c>
+      <c r="E71" t="n">
         <v>168</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>176</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <v>-3.45</v>
       </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3702,33 +3909,36 @@
         <v>7175</v>
       </c>
       <c r="D72" t="n">
-        <v>7200</v>
+        <v>7175</v>
       </c>
       <c r="E72" t="n">
         <v>7200</v>
       </c>
-      <c r="F72" s="4" t="n">
-        <v>0.35</v>
+      <c r="F72" t="n">
+        <v>7200</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H72" s="4" t="n">
+        <v>0.35</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3749,33 +3959,36 @@
         <v>585</v>
       </c>
       <c r="D73" t="n">
+        <v>585</v>
+      </c>
+      <c r="E73" t="n">
         <v>615</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>620</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>5.98</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <v>5.13</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3792,7 +4005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3800,12 +4013,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3835,45 +4049,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
